--- a/out/ma_deals_AUDIT.xlsx
+++ b/out/ma_deals_AUDIT.xlsx
@@ -3775,625 +3775,625 @@
     <t>3.12.9</t>
   </si>
   <si>
-    <t>2026-03-29T16:48:05.066721+03:00</t>
-  </si>
-  <si>
-    <t>2026-03-29T16:48:05.072671+03:00</t>
-  </si>
-  <si>
-    <t>2026-03-29T16:48:05.076786+03:00</t>
-  </si>
-  <si>
-    <t>2026-03-29T16:48:05.082316+03:00</t>
-  </si>
-  <si>
-    <t>2026-03-29T16:48:05.087945+03:00</t>
-  </si>
-  <si>
-    <t>2026-03-29T16:48:05.091649+03:00</t>
-  </si>
-  <si>
-    <t>2026-03-29T16:48:05.096088+03:00</t>
-  </si>
-  <si>
-    <t>2026-03-29T16:48:05.146672+03:00</t>
-  </si>
-  <si>
-    <t>2026-03-29T16:48:05.151452+03:00</t>
-  </si>
-  <si>
-    <t>2026-03-29T16:48:05.159794+03:00</t>
-  </si>
-  <si>
-    <t>2026-03-29T16:48:05.163509+03:00</t>
-  </si>
-  <si>
-    <t>2026-03-29T16:48:05.168836+03:00</t>
-  </si>
-  <si>
-    <t>2026-03-29T16:48:05.173833+03:00</t>
-  </si>
-  <si>
-    <t>2026-03-29T16:48:05.177449+03:00</t>
-  </si>
-  <si>
-    <t>2026-03-29T16:48:05.182078+03:00</t>
-  </si>
-  <si>
-    <t>2026-03-29T16:48:05.190422+03:00</t>
-  </si>
-  <si>
-    <t>2026-03-29T16:48:05.194815+03:00</t>
-  </si>
-  <si>
-    <t>2026-03-29T16:48:05.199584+03:00</t>
-  </si>
-  <si>
-    <t>2026-03-29T16:48:05.207121+03:00</t>
-  </si>
-  <si>
-    <t>2026-03-29T16:48:05.211803+03:00</t>
-  </si>
-  <si>
-    <t>2026-03-29T16:48:05.214146+03:00</t>
-  </si>
-  <si>
-    <t>2026-03-29T16:48:05.218929+03:00</t>
-  </si>
-  <si>
-    <t>2026-03-29T16:48:05.226188+03:00</t>
-  </si>
-  <si>
-    <t>2026-03-29T16:48:05.235952+03:00</t>
-  </si>
-  <si>
-    <t>2026-03-29T16:48:05.246192+03:00</t>
-  </si>
-  <si>
-    <t>2026-03-29T16:48:05.258167+03:00</t>
-  </si>
-  <si>
-    <t>2026-03-29T16:48:05.263190+03:00</t>
-  </si>
-  <si>
-    <t>2026-03-29T16:48:05.269709+03:00</t>
-  </si>
-  <si>
-    <t>2026-03-29T16:48:05.274391+03:00</t>
-  </si>
-  <si>
-    <t>2026-03-29T16:48:05.277632+03:00</t>
-  </si>
-  <si>
-    <t>2026-03-29T16:48:05.281245+03:00</t>
-  </si>
-  <si>
-    <t>2026-03-29T16:48:05.286844+03:00</t>
-  </si>
-  <si>
-    <t>2026-03-29T16:48:05.291736+03:00</t>
-  </si>
-  <si>
-    <t>2026-03-29T16:48:05.295331+03:00</t>
-  </si>
-  <si>
-    <t>2026-03-29T16:48:05.300305+03:00</t>
-  </si>
-  <si>
-    <t>2026-03-29T16:48:05.308155+03:00</t>
-  </si>
-  <si>
-    <t>2026-03-29T16:48:05.311850+03:00</t>
-  </si>
-  <si>
-    <t>2026-03-29T16:48:05.313931+03:00</t>
-  </si>
-  <si>
-    <t>2026-03-29T16:48:05.324336+03:00</t>
-  </si>
-  <si>
-    <t>2026-03-29T16:48:05.326583+03:00</t>
-  </si>
-  <si>
-    <t>2026-03-29T16:48:05.329471+03:00</t>
-  </si>
-  <si>
-    <t>2026-03-29T16:48:05.336955+03:00</t>
-  </si>
-  <si>
-    <t>2026-03-29T16:48:05.343552+03:00</t>
-  </si>
-  <si>
-    <t>2026-03-29T16:48:05.346374+03:00</t>
-  </si>
-  <si>
-    <t>2026-03-29T16:48:05.353882+03:00</t>
-  </si>
-  <si>
-    <t>2026-03-29T16:48:05.357140+03:00</t>
-  </si>
-  <si>
-    <t>2026-03-29T16:48:05.361496+03:00</t>
-  </si>
-  <si>
-    <t>2026-03-29T16:48:05.367497+03:00</t>
-  </si>
-  <si>
-    <t>2026-03-29T16:48:05.375510+03:00</t>
-  </si>
-  <si>
-    <t>2026-03-29T16:48:05.379465+03:00</t>
-  </si>
-  <si>
-    <t>2026-03-29T16:48:05.387658+03:00</t>
-  </si>
-  <si>
-    <t>2026-03-29T16:48:05.392606+03:00</t>
-  </si>
-  <si>
-    <t>2026-03-29T16:48:05.396174+03:00</t>
-  </si>
-  <si>
-    <t>2026-03-29T16:48:05.403437+03:00</t>
-  </si>
-  <si>
-    <t>2026-03-29T16:48:05.409613+03:00</t>
-  </si>
-  <si>
-    <t>2026-03-29T16:48:05.412460+03:00</t>
-  </si>
-  <si>
-    <t>2026-03-29T16:48:05.419938+03:00</t>
-  </si>
-  <si>
-    <t>2026-03-29T16:48:05.426246+03:00</t>
-  </si>
-  <si>
-    <t>2026-03-29T16:48:05.429727+03:00</t>
-  </si>
-  <si>
-    <t>2026-03-29T16:48:05.437812+03:00</t>
-  </si>
-  <si>
-    <t>2026-03-29T16:48:05.443222+03:00</t>
-  </si>
-  <si>
-    <t>2026-03-29T16:48:05.446004+03:00</t>
-  </si>
-  <si>
-    <t>2026-03-29T16:48:05.452333+03:00</t>
-  </si>
-  <si>
-    <t>2026-03-29T16:48:05.459241+03:00</t>
-  </si>
-  <si>
-    <t>2026-03-29T16:48:05.463961+03:00</t>
-  </si>
-  <si>
-    <t>2026-03-29T16:48:05.470608+03:00</t>
-  </si>
-  <si>
-    <t>2026-03-29T16:48:05.476872+03:00</t>
-  </si>
-  <si>
-    <t>2026-03-29T16:48:05.480902+03:00</t>
-  </si>
-  <si>
-    <t>2026-03-29T16:48:05.487426+03:00</t>
-  </si>
-  <si>
-    <t>2026-03-29T16:48:05.492829+03:00</t>
-  </si>
-  <si>
-    <t>2026-03-29T16:48:05.497065+03:00</t>
-  </si>
-  <si>
-    <t>2026-03-29T16:48:05.506545+03:00</t>
-  </si>
-  <si>
-    <t>2026-03-29T16:48:05.510006+03:00</t>
-  </si>
-  <si>
-    <t>2026-03-29T16:48:05.513485+03:00</t>
-  </si>
-  <si>
-    <t>2026-03-29T16:48:05.522201+03:00</t>
-  </si>
-  <si>
-    <t>2026-03-29T16:48:05.526543+03:00</t>
-  </si>
-  <si>
-    <t>2026-03-29T16:48:05.530049+03:00</t>
-  </si>
-  <si>
-    <t>2026-03-29T16:48:05.538909+03:00</t>
-  </si>
-  <si>
-    <t>2026-03-29T16:48:05.543431+03:00</t>
-  </si>
-  <si>
-    <t>2026-03-29T16:48:05.546729+03:00</t>
-  </si>
-  <si>
-    <t>2026-03-29T16:48:05.556272+03:00</t>
-  </si>
-  <si>
-    <t>2026-03-29T16:48:05.561096+03:00</t>
-  </si>
-  <si>
-    <t>2026-03-29T16:48:05.565444+03:00</t>
-  </si>
-  <si>
-    <t>2026-03-29T16:48:05.574965+03:00</t>
-  </si>
-  <si>
-    <t>2026-03-29T16:48:05.577859+03:00</t>
-  </si>
-  <si>
-    <t>2026-03-29T16:48:05.580469+03:00</t>
-  </si>
-  <si>
-    <t>2026-03-29T16:48:05.588500+03:00</t>
-  </si>
-  <si>
-    <t>2026-03-29T16:48:05.592860+03:00</t>
-  </si>
-  <si>
-    <t>2026-03-29T16:48:05.595707+03:00</t>
-  </si>
-  <si>
-    <t>2026-03-29T16:48:05.600939+03:00</t>
-  </si>
-  <si>
-    <t>2026-03-29T16:48:05.608394+03:00</t>
-  </si>
-  <si>
-    <t>2026-03-29T16:48:05.612409+03:00</t>
-  </si>
-  <si>
-    <t>2026-03-29T16:48:05.621671+03:00</t>
-  </si>
-  <si>
-    <t>2026-03-29T16:48:05.626215+03:00</t>
-  </si>
-  <si>
-    <t>2026-03-29T16:48:05.629500+03:00</t>
-  </si>
-  <si>
-    <t>2026-03-29T16:48:05.637758+03:00</t>
-  </si>
-  <si>
-    <t>2026-03-29T16:48:05.643522+03:00</t>
-  </si>
-  <si>
-    <t>2026-03-29T16:48:05.646811+03:00</t>
-  </si>
-  <si>
-    <t>2026-03-29T16:48:05.655764+03:00</t>
-  </si>
-  <si>
-    <t>2026-03-29T16:48:05.660322+03:00</t>
-  </si>
-  <si>
-    <t>2026-03-29T16:48:05.663218+03:00</t>
-  </si>
-  <si>
-    <t>2026-03-29T16:48:05.669580+03:00</t>
-  </si>
-  <si>
-    <t>2026-03-29T16:48:05.673835+03:00</t>
-  </si>
-  <si>
-    <t>2026-03-29T16:48:05.679191+03:00</t>
-  </si>
-  <si>
-    <t>2026-03-29T16:48:05.683116+03:00</t>
-  </si>
-  <si>
-    <t>2026-03-29T16:48:05.689919+03:00</t>
-  </si>
-  <si>
-    <t>2026-03-29T16:48:05.693734+03:00</t>
-  </si>
-  <si>
-    <t>2026-03-29T16:48:05.695727+03:00</t>
-  </si>
-  <si>
-    <t>2026-03-29T16:48:05.703213+03:00</t>
-  </si>
-  <si>
-    <t>2026-03-29T16:48:05.705881+03:00</t>
-  </si>
-  <si>
-    <t>2026-03-29T16:48:05.710927+03:00</t>
-  </si>
-  <si>
-    <t>2026-03-29T16:48:05.714789+03:00</t>
-  </si>
-  <si>
-    <t>2026-03-29T16:48:05.723551+03:00</t>
-  </si>
-  <si>
-    <t>2026-03-29T16:48:05.727453+03:00</t>
-  </si>
-  <si>
-    <t>2026-03-29T16:48:05.730629+03:00</t>
-  </si>
-  <si>
-    <t>2026-03-29T16:48:05.740365+03:00</t>
-  </si>
-  <si>
-    <t>2026-03-29T16:48:05.744058+03:00</t>
-  </si>
-  <si>
-    <t>2026-03-29T16:48:05.747213+03:00</t>
-  </si>
-  <si>
-    <t>2026-03-29T16:48:05.756637+03:00</t>
-  </si>
-  <si>
-    <t>2026-03-29T16:48:05.760295+03:00</t>
-  </si>
-  <si>
-    <t>2026-03-29T16:48:05.763299+03:00</t>
-  </si>
-  <si>
-    <t>2026-03-29T16:48:05.770235+03:00</t>
-  </si>
-  <si>
-    <t>2026-03-29T16:48:05.776049+03:00</t>
-  </si>
-  <si>
-    <t>2026-03-29T16:48:05.778875+03:00</t>
-  </si>
-  <si>
-    <t>2026-03-29T16:48:05.783313+03:00</t>
-  </si>
-  <si>
-    <t>2026-03-29T16:48:05.791178+03:00</t>
-  </si>
-  <si>
-    <t>2026-03-29T16:48:05.794152+03:00</t>
-  </si>
-  <si>
-    <t>2026-03-29T16:48:05.797036+03:00</t>
-  </si>
-  <si>
-    <t>2026-03-29T16:48:05.803705+03:00</t>
-  </si>
-  <si>
-    <t>2026-03-29T16:48:05.807436+03:00</t>
-  </si>
-  <si>
-    <t>2026-03-29T16:48:05.812817+03:00</t>
-  </si>
-  <si>
-    <t>2026-03-29T16:48:05.817697+03:00</t>
-  </si>
-  <si>
-    <t>2026-03-29T16:48:05.823967+03:00</t>
-  </si>
-  <si>
-    <t>2026-03-29T16:48:05.826595+03:00</t>
-  </si>
-  <si>
-    <t>2026-03-29T16:48:05.828902+03:00</t>
-  </si>
-  <si>
-    <t>2026-03-29T16:48:05.831486+03:00</t>
-  </si>
-  <si>
-    <t>2026-03-29T16:48:05.837285+03:00</t>
-  </si>
-  <si>
-    <t>2026-03-29T16:48:05.842931+03:00</t>
-  </si>
-  <si>
-    <t>2026-03-29T16:48:05.845330+03:00</t>
-  </si>
-  <si>
-    <t>2026-03-29T16:48:05.847402+03:00</t>
-  </si>
-  <si>
-    <t>2026-03-29T16:48:05.855603+03:00</t>
-  </si>
-  <si>
-    <t>2026-03-29T16:48:05.860628+03:00</t>
-  </si>
-  <si>
-    <t>2026-03-29T16:48:05.867615+03:00</t>
-  </si>
-  <si>
-    <t>2026-03-29T16:48:05.876240+03:00</t>
-  </si>
-  <si>
-    <t>2026-03-29T16:48:05.881831+03:00</t>
-  </si>
-  <si>
-    <t>2026-03-29T16:48:05.890319+03:00</t>
-  </si>
-  <si>
-    <t>2026-03-29T16:48:05.894998+03:00</t>
-  </si>
-  <si>
-    <t>2026-03-29T16:48:05.897456+03:00</t>
-  </si>
-  <si>
-    <t>2026-03-29T16:48:05.907079+03:00</t>
-  </si>
-  <si>
-    <t>2026-03-29T16:48:05.910563+03:00</t>
-  </si>
-  <si>
-    <t>2026-03-29T16:48:05.914153+03:00</t>
-  </si>
-  <si>
-    <t>2026-03-29T16:48:05.919951+03:00</t>
-  </si>
-  <si>
-    <t>2026-03-29T16:48:05.925538+03:00</t>
-  </si>
-  <si>
-    <t>2026-03-29T16:48:05.928599+03:00</t>
-  </si>
-  <si>
-    <t>2026-03-29T16:48:05.934046+03:00</t>
-  </si>
-  <si>
-    <t>2026-03-29T16:48:05.940714+03:00</t>
-  </si>
-  <si>
-    <t>2026-03-29T16:48:05.943931+03:00</t>
-  </si>
-  <si>
-    <t>2026-03-29T16:48:05.947198+03:00</t>
-  </si>
-  <si>
-    <t>2026-03-29T16:48:05.955447+03:00</t>
-  </si>
-  <si>
-    <t>2026-03-29T16:48:05.959621+03:00</t>
-  </si>
-  <si>
-    <t>2026-03-29T16:48:05.963006+03:00</t>
-  </si>
-  <si>
-    <t>2026-03-29T16:48:05.972495+03:00</t>
-  </si>
-  <si>
-    <t>2026-03-29T16:48:05.977607+03:00</t>
-  </si>
-  <si>
-    <t>2026-03-29T16:48:05.980812+03:00</t>
-  </si>
-  <si>
-    <t>2026-03-29T16:48:05.990456+03:00</t>
-  </si>
-  <si>
-    <t>2026-03-29T16:48:05.993110+03:00</t>
-  </si>
-  <si>
-    <t>2026-03-29T16:48:05.996655+03:00</t>
-  </si>
-  <si>
-    <t>2026-03-29T16:48:06.000286+03:00</t>
-  </si>
-  <si>
-    <t>2026-03-29T16:48:06.008331+03:00</t>
-  </si>
-  <si>
-    <t>2026-03-29T16:48:06.011602+03:00</t>
-  </si>
-  <si>
-    <t>2026-03-29T16:48:06.016264+03:00</t>
-  </si>
-  <si>
-    <t>2026-03-29T16:48:06.024825+03:00</t>
-  </si>
-  <si>
-    <t>2026-03-29T16:48:06.027971+03:00</t>
-  </si>
-  <si>
-    <t>2026-03-29T16:48:06.031295+03:00</t>
-  </si>
-  <si>
-    <t>2026-03-29T16:48:06.040566+03:00</t>
-  </si>
-  <si>
-    <t>2026-03-29T16:48:06.044591+03:00</t>
-  </si>
-  <si>
-    <t>2026-03-29T16:48:06.048970+03:00</t>
-  </si>
-  <si>
-    <t>2026-03-29T16:48:06.057866+03:00</t>
-  </si>
-  <si>
-    <t>2026-03-29T16:48:06.060912+03:00</t>
-  </si>
-  <si>
-    <t>2026-03-29T16:48:06.063538+03:00</t>
-  </si>
-  <si>
-    <t>2026-03-29T16:48:06.071194+03:00</t>
-  </si>
-  <si>
-    <t>2026-03-29T16:48:06.074464+03:00</t>
-  </si>
-  <si>
-    <t>2026-03-29T16:48:06.079822+03:00</t>
-  </si>
-  <si>
-    <t>2026-03-29T16:48:06.087575+03:00</t>
-  </si>
-  <si>
-    <t>2026-03-29T16:48:06.093066+03:00</t>
-  </si>
-  <si>
-    <t>2026-03-29T16:48:06.096399+03:00</t>
-  </si>
-  <si>
-    <t>2026-03-29T16:48:06.104435+03:00</t>
-  </si>
-  <si>
-    <t>2026-03-29T16:48:06.110232+03:00</t>
-  </si>
-  <si>
-    <t>2026-03-29T16:48:06.113772+03:00</t>
-  </si>
-  <si>
-    <t>2026-03-29T16:48:06.119905+03:00</t>
-  </si>
-  <si>
-    <t>2026-03-29T16:48:06.125097+03:00</t>
-  </si>
-  <si>
-    <t>2026-03-29T16:48:06.128509+03:00</t>
-  </si>
-  <si>
-    <t>2026-03-29T16:48:06.134359+03:00</t>
-  </si>
-  <si>
-    <t>2026-03-29T16:48:06.141815+03:00</t>
-  </si>
-  <si>
-    <t>2026-03-29T16:48:06.144452+03:00</t>
-  </si>
-  <si>
-    <t>2026-03-29T16:48:06.147044+03:00</t>
-  </si>
-  <si>
-    <t>2026-03-29T16:48:06.153206+03:00</t>
-  </si>
-  <si>
-    <t>2026-03-29T16:48:06.158872+03:00</t>
-  </si>
-  <si>
-    <t>2026-03-29T16:48:06.162065+03:00</t>
-  </si>
-  <si>
-    <t>2026-03-29T16:48:06.168082+03:00</t>
-  </si>
-  <si>
-    <t>2026-03-29T16:48:06.174329+03:00</t>
-  </si>
-  <si>
-    <t>2026-03-29T16:48:06.177553+03:00</t>
-  </si>
-  <si>
-    <t>2026-03-29T16:48:06.180892+03:00</t>
-  </si>
-  <si>
-    <t>2026-03-29T16:48:06.187528+03:00</t>
-  </si>
-  <si>
-    <t>2026-03-29T16:48:06.193142+03:00</t>
-  </si>
-  <si>
-    <t>2026-03-29T16:48:06.195919+03:00</t>
-  </si>
-  <si>
-    <t>2026-03-29T16:48:06.202843+03:00</t>
+    <t>2026-03-29T17:15:53.136396+03:00</t>
+  </si>
+  <si>
+    <t>2026-03-29T17:15:53.141238+03:00</t>
+  </si>
+  <si>
+    <t>2026-03-29T17:15:53.144445+03:00</t>
+  </si>
+  <si>
+    <t>2026-03-29T17:15:53.150271+03:00</t>
+  </si>
+  <si>
+    <t>2026-03-29T17:15:53.154896+03:00</t>
+  </si>
+  <si>
+    <t>2026-03-29T17:15:53.158113+03:00</t>
+  </si>
+  <si>
+    <t>2026-03-29T17:15:53.160120+03:00</t>
+  </si>
+  <si>
+    <t>2026-03-29T17:15:53.162521+03:00</t>
+  </si>
+  <si>
+    <t>2026-03-29T17:15:53.223512+03:00</t>
+  </si>
+  <si>
+    <t>2026-03-29T17:15:53.225845+03:00</t>
+  </si>
+  <si>
+    <t>2026-03-29T17:15:53.227658+03:00</t>
+  </si>
+  <si>
+    <t>2026-03-29T17:15:53.229863+03:00</t>
+  </si>
+  <si>
+    <t>2026-03-29T17:15:53.231904+03:00</t>
+  </si>
+  <si>
+    <t>2026-03-29T17:15:53.233781+03:00</t>
+  </si>
+  <si>
+    <t>2026-03-29T17:15:53.236953+03:00</t>
+  </si>
+  <si>
+    <t>2026-03-29T17:15:53.239641+03:00</t>
+  </si>
+  <si>
+    <t>2026-03-29T17:15:53.242672+03:00</t>
+  </si>
+  <si>
+    <t>2026-03-29T17:15:53.244530+03:00</t>
+  </si>
+  <si>
+    <t>2026-03-29T17:15:53.245805+03:00</t>
+  </si>
+  <si>
+    <t>2026-03-29T17:15:53.247223+03:00</t>
+  </si>
+  <si>
+    <t>2026-03-29T17:15:53.248006+03:00</t>
+  </si>
+  <si>
+    <t>2026-03-29T17:15:53.248521+03:00</t>
+  </si>
+  <si>
+    <t>2026-03-29T17:15:53.249781+03:00</t>
+  </si>
+  <si>
+    <t>2026-03-29T17:15:53.251759+03:00</t>
+  </si>
+  <si>
+    <t>2026-03-29T17:15:53.253754+03:00</t>
+  </si>
+  <si>
+    <t>2026-03-29T17:15:53.257403+03:00</t>
+  </si>
+  <si>
+    <t>2026-03-29T17:15:53.259904+03:00</t>
+  </si>
+  <si>
+    <t>2026-03-29T17:15:53.260925+03:00</t>
+  </si>
+  <si>
+    <t>2026-03-29T17:15:53.261501+03:00</t>
+  </si>
+  <si>
+    <t>2026-03-29T17:15:53.262125+03:00</t>
+  </si>
+  <si>
+    <t>2026-03-29T17:15:53.263136+03:00</t>
+  </si>
+  <si>
+    <t>2026-03-29T17:15:53.263784+03:00</t>
+  </si>
+  <si>
+    <t>2026-03-29T17:15:53.264424+03:00</t>
+  </si>
+  <si>
+    <t>2026-03-29T17:15:53.265392+03:00</t>
+  </si>
+  <si>
+    <t>2026-03-29T17:15:53.266435+03:00</t>
+  </si>
+  <si>
+    <t>2026-03-29T17:15:53.268655+03:00</t>
+  </si>
+  <si>
+    <t>2026-03-29T17:15:53.270367+03:00</t>
+  </si>
+  <si>
+    <t>2026-03-29T17:15:53.271699+03:00</t>
+  </si>
+  <si>
+    <t>2026-03-29T17:15:53.273983+03:00</t>
+  </si>
+  <si>
+    <t>2026-03-29T17:15:53.274835+03:00</t>
+  </si>
+  <si>
+    <t>2026-03-29T17:15:53.275850+03:00</t>
+  </si>
+  <si>
+    <t>2026-03-29T17:15:53.278297+03:00</t>
+  </si>
+  <si>
+    <t>2026-03-29T17:15:53.279429+03:00</t>
+  </si>
+  <si>
+    <t>2026-03-29T17:15:53.280046+03:00</t>
+  </si>
+  <si>
+    <t>2026-03-29T17:15:53.281211+03:00</t>
+  </si>
+  <si>
+    <t>2026-03-29T17:15:53.281885+03:00</t>
+  </si>
+  <si>
+    <t>2026-03-29T17:15:53.282474+03:00</t>
+  </si>
+  <si>
+    <t>2026-03-29T17:15:53.283555+03:00</t>
+  </si>
+  <si>
+    <t>2026-03-29T17:15:53.287371+03:00</t>
+  </si>
+  <si>
+    <t>2026-03-29T17:15:53.290736+03:00</t>
+  </si>
+  <si>
+    <t>2026-03-29T17:15:53.294120+03:00</t>
+  </si>
+  <si>
+    <t>2026-03-29T17:15:53.294816+03:00</t>
+  </si>
+  <si>
+    <t>2026-03-29T17:15:53.296050+03:00</t>
+  </si>
+  <si>
+    <t>2026-03-29T17:15:53.297223+03:00</t>
+  </si>
+  <si>
+    <t>2026-03-29T17:15:53.298125+03:00</t>
+  </si>
+  <si>
+    <t>2026-03-29T17:15:53.298845+03:00</t>
+  </si>
+  <si>
+    <t>2026-03-29T17:15:53.300947+03:00</t>
+  </si>
+  <si>
+    <t>2026-03-29T17:15:53.304915+03:00</t>
+  </si>
+  <si>
+    <t>2026-03-29T17:15:53.306852+03:00</t>
+  </si>
+  <si>
+    <t>2026-03-29T17:15:53.310204+03:00</t>
+  </si>
+  <si>
+    <t>2026-03-29T17:15:53.311806+03:00</t>
+  </si>
+  <si>
+    <t>2026-03-29T17:15:53.312483+03:00</t>
+  </si>
+  <si>
+    <t>2026-03-29T17:15:53.313156+03:00</t>
+  </si>
+  <si>
+    <t>2026-03-29T17:15:53.314374+03:00</t>
+  </si>
+  <si>
+    <t>2026-03-29T17:15:53.315783+03:00</t>
+  </si>
+  <si>
+    <t>2026-03-29T17:15:53.316315+03:00</t>
+  </si>
+  <si>
+    <t>2026-03-29T17:15:53.318715+03:00</t>
+  </si>
+  <si>
+    <t>2026-03-29T17:15:53.321915+03:00</t>
+  </si>
+  <si>
+    <t>2026-03-29T17:15:53.322915+03:00</t>
+  </si>
+  <si>
+    <t>2026-03-29T17:15:53.324702+03:00</t>
+  </si>
+  <si>
+    <t>2026-03-29T17:15:53.326505+03:00</t>
+  </si>
+  <si>
+    <t>2026-03-29T17:15:53.327920+03:00</t>
+  </si>
+  <si>
+    <t>2026-03-29T17:15:53.328574+03:00</t>
+  </si>
+  <si>
+    <t>2026-03-29T17:15:53.329764+03:00</t>
+  </si>
+  <si>
+    <t>2026-03-29T17:15:53.330857+03:00</t>
+  </si>
+  <si>
+    <t>2026-03-29T17:15:53.331561+03:00</t>
+  </si>
+  <si>
+    <t>2026-03-29T17:15:53.332636+03:00</t>
+  </si>
+  <si>
+    <t>2026-03-29T17:15:53.335131+03:00</t>
+  </si>
+  <si>
+    <t>2026-03-29T17:15:53.338525+03:00</t>
+  </si>
+  <si>
+    <t>2026-03-29T17:15:53.341655+03:00</t>
+  </si>
+  <si>
+    <t>2026-03-29T17:15:53.343113+03:00</t>
+  </si>
+  <si>
+    <t>2026-03-29T17:15:53.344168+03:00</t>
+  </si>
+  <si>
+    <t>2026-03-29T17:15:53.345114+03:00</t>
+  </si>
+  <si>
+    <t>2026-03-29T17:15:53.346147+03:00</t>
+  </si>
+  <si>
+    <t>2026-03-29T17:15:53.346756+03:00</t>
+  </si>
+  <si>
+    <t>2026-03-29T17:15:53.347353+03:00</t>
+  </si>
+  <si>
+    <t>2026-03-29T17:15:53.347941+03:00</t>
+  </si>
+  <si>
+    <t>2026-03-29T17:15:53.348488+03:00</t>
+  </si>
+  <si>
+    <t>2026-03-29T17:15:53.349110+03:00</t>
+  </si>
+  <si>
+    <t>2026-03-29T17:15:53.349742+03:00</t>
+  </si>
+  <si>
+    <t>2026-03-29T17:15:53.352536+03:00</t>
+  </si>
+  <si>
+    <t>2026-03-29T17:15:53.355752+03:00</t>
+  </si>
+  <si>
+    <t>2026-03-29T17:15:53.358496+03:00</t>
+  </si>
+  <si>
+    <t>2026-03-29T17:15:53.359350+03:00</t>
+  </si>
+  <si>
+    <t>2026-03-29T17:15:53.360450+03:00</t>
+  </si>
+  <si>
+    <t>2026-03-29T17:15:53.361895+03:00</t>
+  </si>
+  <si>
+    <t>2026-03-29T17:15:53.362979+03:00</t>
+  </si>
+  <si>
+    <t>2026-03-29T17:15:53.363596+03:00</t>
+  </si>
+  <si>
+    <t>2026-03-29T17:15:53.364506+03:00</t>
+  </si>
+  <si>
+    <t>2026-03-29T17:15:53.365393+03:00</t>
+  </si>
+  <si>
+    <t>2026-03-29T17:15:53.366106+03:00</t>
+  </si>
+  <si>
+    <t>2026-03-29T17:15:53.366839+03:00</t>
+  </si>
+  <si>
+    <t>2026-03-29T17:15:53.368553+03:00</t>
+  </si>
+  <si>
+    <t>2026-03-29T17:15:53.371638+03:00</t>
+  </si>
+  <si>
+    <t>2026-03-29T17:15:53.373061+03:00</t>
+  </si>
+  <si>
+    <t>2026-03-29T17:15:53.374565+03:00</t>
+  </si>
+  <si>
+    <t>2026-03-29T17:15:53.376382+03:00</t>
+  </si>
+  <si>
+    <t>2026-03-29T17:15:53.377061+03:00</t>
+  </si>
+  <si>
+    <t>2026-03-29T17:15:53.378306+03:00</t>
+  </si>
+  <si>
+    <t>2026-03-29T17:15:53.378860+03:00</t>
+  </si>
+  <si>
+    <t>2026-03-29T17:15:53.379719+03:00</t>
+  </si>
+  <si>
+    <t>2026-03-29T17:15:53.380658+03:00</t>
+  </si>
+  <si>
+    <t>2026-03-29T17:15:53.381285+03:00</t>
+  </si>
+  <si>
+    <t>2026-03-29T17:15:53.381848+03:00</t>
+  </si>
+  <si>
+    <t>2026-03-29T17:15:53.382668+03:00</t>
+  </si>
+  <si>
+    <t>2026-03-29T17:15:53.383986+03:00</t>
+  </si>
+  <si>
+    <t>2026-03-29T17:15:53.387088+03:00</t>
+  </si>
+  <si>
+    <t>2026-03-29T17:15:53.389381+03:00</t>
+  </si>
+  <si>
+    <t>2026-03-29T17:15:53.391935+03:00</t>
+  </si>
+  <si>
+    <t>2026-03-29T17:15:53.393037+03:00</t>
+  </si>
+  <si>
+    <t>2026-03-29T17:15:53.393870+03:00</t>
+  </si>
+  <si>
+    <t>2026-03-29T17:15:53.394492+03:00</t>
+  </si>
+  <si>
+    <t>2026-03-29T17:15:53.395405+03:00</t>
+  </si>
+  <si>
+    <t>2026-03-29T17:15:53.396092+03:00</t>
+  </si>
+  <si>
+    <t>2026-03-29T17:15:53.396739+03:00</t>
+  </si>
+  <si>
+    <t>2026-03-29T17:15:53.397458+03:00</t>
+  </si>
+  <si>
+    <t>2026-03-29T17:15:53.398038+03:00</t>
+  </si>
+  <si>
+    <t>2026-03-29T17:15:53.398700+03:00</t>
+  </si>
+  <si>
+    <t>2026-03-29T17:15:53.399298+03:00</t>
+  </si>
+  <si>
+    <t>2026-03-29T17:15:53.400497+03:00</t>
+  </si>
+  <si>
+    <t>2026-03-29T17:15:53.402971+03:00</t>
+  </si>
+  <si>
+    <t>2026-03-29T17:15:53.405560+03:00</t>
+  </si>
+  <si>
+    <t>2026-03-29T17:15:53.407475+03:00</t>
+  </si>
+  <si>
+    <t>2026-03-29T17:15:53.409338+03:00</t>
+  </si>
+  <si>
+    <t>2026-03-29T17:15:53.410460+03:00</t>
+  </si>
+  <si>
+    <t>2026-03-29T17:15:53.411427+03:00</t>
+  </si>
+  <si>
+    <t>2026-03-29T17:15:53.412126+03:00</t>
+  </si>
+  <si>
+    <t>2026-03-29T17:15:53.413393+03:00</t>
+  </si>
+  <si>
+    <t>2026-03-29T17:15:53.414187+03:00</t>
+  </si>
+  <si>
+    <t>2026-03-29T17:15:53.414742+03:00</t>
+  </si>
+  <si>
+    <t>2026-03-29T17:15:53.415388+03:00</t>
+  </si>
+  <si>
+    <t>2026-03-29T17:15:53.416329+03:00</t>
+  </si>
+  <si>
+    <t>2026-03-29T17:15:53.417466+03:00</t>
+  </si>
+  <si>
+    <t>2026-03-29T17:15:53.418883+03:00</t>
+  </si>
+  <si>
+    <t>2026-03-29T17:15:53.421069+03:00</t>
+  </si>
+  <si>
+    <t>2026-03-29T17:15:53.422950+03:00</t>
+  </si>
+  <si>
+    <t>2026-03-29T17:15:53.425692+03:00</t>
+  </si>
+  <si>
+    <t>2026-03-29T17:15:53.426481+03:00</t>
+  </si>
+  <si>
+    <t>2026-03-29T17:15:53.427429+03:00</t>
+  </si>
+  <si>
+    <t>2026-03-29T17:15:53.428305+03:00</t>
+  </si>
+  <si>
+    <t>2026-03-29T17:15:53.429483+03:00</t>
+  </si>
+  <si>
+    <t>2026-03-29T17:15:53.430073+03:00</t>
+  </si>
+  <si>
+    <t>2026-03-29T17:15:53.430895+03:00</t>
+  </si>
+  <si>
+    <t>2026-03-29T17:15:53.431715+03:00</t>
+  </si>
+  <si>
+    <t>2026-03-29T17:15:53.432574+03:00</t>
+  </si>
+  <si>
+    <t>2026-03-29T17:15:53.433187+03:00</t>
+  </si>
+  <si>
+    <t>2026-03-29T17:15:53.435799+03:00</t>
+  </si>
+  <si>
+    <t>2026-03-29T17:15:53.438830+03:00</t>
+  </si>
+  <si>
+    <t>2026-03-29T17:15:53.441141+03:00</t>
+  </si>
+  <si>
+    <t>2026-03-29T17:15:53.442300+03:00</t>
+  </si>
+  <si>
+    <t>2026-03-29T17:15:53.443267+03:00</t>
+  </si>
+  <si>
+    <t>2026-03-29T17:15:53.444151+03:00</t>
+  </si>
+  <si>
+    <t>2026-03-29T17:15:53.445211+03:00</t>
+  </si>
+  <si>
+    <t>2026-03-29T17:15:53.445781+03:00</t>
+  </si>
+  <si>
+    <t>2026-03-29T17:15:53.446819+03:00</t>
+  </si>
+  <si>
+    <t>2026-03-29T17:15:53.447454+03:00</t>
+  </si>
+  <si>
+    <t>2026-03-29T17:15:53.448510+03:00</t>
+  </si>
+  <si>
+    <t>2026-03-29T17:15:53.449127+03:00</t>
+  </si>
+  <si>
+    <t>2026-03-29T17:15:53.451942+03:00</t>
+  </si>
+  <si>
+    <t>2026-03-29T17:15:53.454853+03:00</t>
+  </si>
+  <si>
+    <t>2026-03-29T17:15:53.456322+03:00</t>
+  </si>
+  <si>
+    <t>2026-03-29T17:15:53.457462+03:00</t>
+  </si>
+  <si>
+    <t>2026-03-29T17:15:53.458664+03:00</t>
+  </si>
+  <si>
+    <t>2026-03-29T17:15:53.460950+03:00</t>
+  </si>
+  <si>
+    <t>2026-03-29T17:15:53.462003+03:00</t>
+  </si>
+  <si>
+    <t>2026-03-29T17:15:53.462973+03:00</t>
+  </si>
+  <si>
+    <t>2026-03-29T17:15:53.463810+03:00</t>
+  </si>
+  <si>
+    <t>2026-03-29T17:15:53.464686+03:00</t>
+  </si>
+  <si>
+    <t>2026-03-29T17:15:53.465406+03:00</t>
+  </si>
+  <si>
+    <t>2026-03-29T17:15:53.466047+03:00</t>
+  </si>
+  <si>
+    <t>2026-03-29T17:15:53.467569+03:00</t>
+  </si>
+  <si>
+    <t>2026-03-29T17:15:53.470969+03:00</t>
+  </si>
+  <si>
+    <t>2026-03-29T17:15:53.473287+03:00</t>
+  </si>
+  <si>
+    <t>2026-03-29T17:15:53.475742+03:00</t>
+  </si>
+  <si>
+    <t>2026-03-29T17:15:53.476778+03:00</t>
+  </si>
+  <si>
+    <t>2026-03-29T17:15:53.477645+03:00</t>
+  </si>
+  <si>
+    <t>2026-03-29T17:15:53.478527+03:00</t>
+  </si>
+  <si>
+    <t>2026-03-29T17:15:53.479537+03:00</t>
+  </si>
+  <si>
+    <t>2026-03-29T17:15:53.480759+03:00</t>
+  </si>
+  <si>
+    <t>2026-03-29T17:15:53.481355+03:00</t>
+  </si>
+  <si>
+    <t>2026-03-29T17:15:53.482232+03:00</t>
+  </si>
+  <si>
+    <t>2026-03-29T17:15:53.483066+03:00</t>
+  </si>
+  <si>
+    <t>2026-03-29T17:15:53.485152+03:00</t>
+  </si>
+  <si>
+    <t>2026-03-29T17:15:53.488890+03:00</t>
+  </si>
+  <si>
+    <t>2026-03-29T17:15:53.490299+03:00</t>
+  </si>
+  <si>
+    <t>2026-03-29T17:15:53.491419+03:00</t>
+  </si>
+  <si>
+    <t>2026-03-29T17:15:53.493252+03:00</t>
+  </si>
+  <si>
+    <t>2026-03-29T17:15:53.495071+03:00</t>
+  </si>
+  <si>
+    <t>2026-03-29T17:15:53.496167+03:00</t>
+  </si>
+  <si>
+    <t>2026-03-29T17:15:53.497119+03:00</t>
+  </si>
+  <si>
+    <t>2026-03-29T17:15:53.497910+03:00</t>
+  </si>
+  <si>
+    <t>2026-03-29T17:15:53.498570+03:00</t>
+  </si>
+  <si>
+    <t>2026-03-29T17:15:53.499413+03:00</t>
+  </si>
+  <si>
+    <t>2026-03-29T17:15:53.500180+03:00</t>
+  </si>
+  <si>
+    <t>2026-03-29T17:15:53.501977+03:00</t>
+  </si>
+  <si>
+    <t>2026-03-29T17:15:53.504169+03:00</t>
+  </si>
+  <si>
+    <t>2026-03-29T17:15:53.506191+03:00</t>
   </si>
 </sst>
 </file>

--- a/out/ma_deals_AUDIT.xlsx
+++ b/out/ma_deals_AUDIT.xlsx
@@ -3796,625 +3796,625 @@
     <t>3.12.9</t>
   </si>
   <si>
-    <t>2026-03-29T18:04:42.878818+03:00</t>
-  </si>
-  <si>
-    <t>2026-03-29T18:04:42.881790+03:00</t>
-  </si>
-  <si>
-    <t>2026-03-29T18:04:42.882496+03:00</t>
-  </si>
-  <si>
-    <t>2026-03-29T18:04:42.884837+03:00</t>
-  </si>
-  <si>
-    <t>2026-03-29T18:04:42.889591+03:00</t>
-  </si>
-  <si>
-    <t>2026-03-29T18:04:42.929139+03:00</t>
-  </si>
-  <si>
-    <t>2026-03-29T18:04:42.932664+03:00</t>
-  </si>
-  <si>
-    <t>2026-03-29T18:04:42.936643+03:00</t>
-  </si>
-  <si>
-    <t>2026-03-29T18:04:42.939168+03:00</t>
-  </si>
-  <si>
-    <t>2026-03-29T18:04:42.941584+03:00</t>
-  </si>
-  <si>
-    <t>2026-03-29T18:04:42.942519+03:00</t>
-  </si>
-  <si>
-    <t>2026-03-29T18:04:42.943293+03:00</t>
-  </si>
-  <si>
-    <t>2026-03-29T18:04:42.944931+03:00</t>
-  </si>
-  <si>
-    <t>2026-03-29T18:04:42.946374+03:00</t>
-  </si>
-  <si>
-    <t>2026-03-29T18:04:42.950535+03:00</t>
-  </si>
-  <si>
-    <t>2026-03-29T18:04:42.955779+03:00</t>
-  </si>
-  <si>
-    <t>2026-03-29T18:04:42.958784+03:00</t>
-  </si>
-  <si>
-    <t>2026-03-29T18:04:42.962738+03:00</t>
-  </si>
-  <si>
-    <t>2026-03-29T18:04:42.966884+03:00</t>
-  </si>
-  <si>
-    <t>2026-03-29T18:04:42.971544+03:00</t>
-  </si>
-  <si>
-    <t>2026-03-29T18:04:42.972452+03:00</t>
-  </si>
-  <si>
-    <t>2026-03-29T18:04:42.973070+03:00</t>
-  </si>
-  <si>
-    <t>2026-03-29T18:04:42.975466+03:00</t>
-  </si>
-  <si>
-    <t>2026-03-29T18:04:42.980162+03:00</t>
-  </si>
-  <si>
-    <t>2026-03-29T18:04:42.987043+03:00</t>
-  </si>
-  <si>
-    <t>2026-03-29T18:04:42.989405+03:00</t>
-  </si>
-  <si>
-    <t>2026-03-29T18:04:42.991750+03:00</t>
-  </si>
-  <si>
-    <t>2026-03-29T18:04:42.994411+03:00</t>
-  </si>
-  <si>
-    <t>2026-03-29T18:04:42.996277+03:00</t>
-  </si>
-  <si>
-    <t>2026-03-29T18:04:43.001333+03:00</t>
-  </si>
-  <si>
-    <t>2026-03-29T18:04:43.002854+03:00</t>
-  </si>
-  <si>
-    <t>2026-03-29T18:04:43.003619+03:00</t>
-  </si>
-  <si>
-    <t>2026-03-29T18:04:43.004495+03:00</t>
-  </si>
-  <si>
-    <t>2026-03-29T18:04:43.006754+03:00</t>
-  </si>
-  <si>
-    <t>2026-03-29T18:04:43.008702+03:00</t>
-  </si>
-  <si>
-    <t>2026-03-29T18:04:43.010507+03:00</t>
-  </si>
-  <si>
-    <t>2026-03-29T18:04:43.013554+03:00</t>
-  </si>
-  <si>
-    <t>2026-03-29T18:04:43.015473+03:00</t>
-  </si>
-  <si>
-    <t>2026-03-29T18:04:43.020444+03:00</t>
-  </si>
-  <si>
-    <t>2026-03-29T18:04:43.021293+03:00</t>
-  </si>
-  <si>
-    <t>2026-03-29T18:04:43.021981+03:00</t>
-  </si>
-  <si>
-    <t>2026-03-29T18:04:43.025057+03:00</t>
-  </si>
-  <si>
-    <t>2026-03-29T18:04:43.027581+03:00</t>
-  </si>
-  <si>
-    <t>2026-03-29T18:04:43.030049+03:00</t>
-  </si>
-  <si>
-    <t>2026-03-29T18:04:43.035484+03:00</t>
-  </si>
-  <si>
-    <t>2026-03-29T18:04:43.036418+03:00</t>
-  </si>
-  <si>
-    <t>2026-03-29T18:04:43.037073+03:00</t>
-  </si>
-  <si>
-    <t>2026-03-29T18:04:43.039095+03:00</t>
-  </si>
-  <si>
-    <t>2026-03-29T18:04:43.041050+03:00</t>
-  </si>
-  <si>
-    <t>2026-03-29T18:04:43.042986+03:00</t>
-  </si>
-  <si>
-    <t>2026-03-29T18:04:43.048274+03:00</t>
-  </si>
-  <si>
-    <t>2026-03-29T18:04:43.049898+03:00</t>
-  </si>
-  <si>
-    <t>2026-03-29T18:04:43.053834+03:00</t>
-  </si>
-  <si>
-    <t>2026-03-29T18:04:43.054669+03:00</t>
-  </si>
-  <si>
-    <t>2026-03-29T18:04:43.055342+03:00</t>
-  </si>
-  <si>
-    <t>2026-03-29T18:04:43.056003+03:00</t>
-  </si>
-  <si>
-    <t>2026-03-29T18:04:43.058115+03:00</t>
-  </si>
-  <si>
-    <t>2026-03-29T18:04:43.068712+03:00</t>
-  </si>
-  <si>
-    <t>2026-03-29T18:04:43.071805+03:00</t>
-  </si>
-  <si>
-    <t>2026-03-29T18:04:43.073899+03:00</t>
-  </si>
-  <si>
-    <t>2026-03-29T18:04:43.075873+03:00</t>
-  </si>
-  <si>
-    <t>2026-03-29T18:04:43.076597+03:00</t>
-  </si>
-  <si>
-    <t>2026-03-29T18:04:43.078634+03:00</t>
-  </si>
-  <si>
-    <t>2026-03-29T18:04:43.084828+03:00</t>
-  </si>
-  <si>
-    <t>2026-03-29T18:04:43.087931+03:00</t>
-  </si>
-  <si>
-    <t>2026-03-29T18:04:43.088606+03:00</t>
-  </si>
-  <si>
-    <t>2026-03-29T18:04:43.091001+03:00</t>
-  </si>
-  <si>
-    <t>2026-03-29T18:04:43.094470+03:00</t>
-  </si>
-  <si>
-    <t>2026-03-29T18:04:43.096349+03:00</t>
-  </si>
-  <si>
-    <t>2026-03-29T18:04:43.098874+03:00</t>
-  </si>
-  <si>
-    <t>2026-03-29T18:04:43.103234+03:00</t>
-  </si>
-  <si>
-    <t>2026-03-29T18:04:43.105343+03:00</t>
-  </si>
-  <si>
-    <t>2026-03-29T18:04:43.106074+03:00</t>
-  </si>
-  <si>
-    <t>2026-03-29T18:04:43.108351+03:00</t>
-  </si>
-  <si>
-    <t>2026-03-29T18:04:43.116848+03:00</t>
-  </si>
-  <si>
-    <t>2026-03-29T18:04:43.117686+03:00</t>
-  </si>
-  <si>
-    <t>2026-03-29T18:04:43.119892+03:00</t>
-  </si>
-  <si>
-    <t>2026-03-29T18:04:43.124356+03:00</t>
-  </si>
-  <si>
-    <t>2026-03-29T18:04:43.126738+03:00</t>
-  </si>
-  <si>
-    <t>2026-03-29T18:04:43.132374+03:00</t>
-  </si>
-  <si>
-    <t>2026-03-29T18:04:43.136379+03:00</t>
-  </si>
-  <si>
-    <t>2026-03-29T18:04:43.138585+03:00</t>
-  </si>
-  <si>
-    <t>2026-03-29T18:04:43.140755+03:00</t>
-  </si>
-  <si>
-    <t>2026-03-29T18:04:43.142824+03:00</t>
-  </si>
-  <si>
-    <t>2026-03-29T18:04:43.143954+03:00</t>
-  </si>
-  <si>
-    <t>2026-03-29T18:04:43.146360+03:00</t>
-  </si>
-  <si>
-    <t>2026-03-29T18:04:43.148640+03:00</t>
-  </si>
-  <si>
-    <t>2026-03-29T18:04:43.150356+03:00</t>
-  </si>
-  <si>
-    <t>2026-03-29T18:04:43.152143+03:00</t>
-  </si>
-  <si>
-    <t>2026-03-29T18:04:43.153023+03:00</t>
-  </si>
-  <si>
-    <t>2026-03-29T18:04:43.155191+03:00</t>
-  </si>
-  <si>
-    <t>2026-03-29T18:04:43.157449+03:00</t>
-  </si>
-  <si>
-    <t>2026-03-29T18:04:43.159523+03:00</t>
-  </si>
-  <si>
-    <t>2026-03-29T18:04:43.160670+03:00</t>
-  </si>
-  <si>
-    <t>2026-03-29T18:04:43.171247+03:00</t>
-  </si>
-  <si>
-    <t>2026-03-29T18:04:43.174507+03:00</t>
-  </si>
-  <si>
-    <t>2026-03-29T18:04:43.177414+03:00</t>
-  </si>
-  <si>
-    <t>2026-03-29T18:04:43.180223+03:00</t>
-  </si>
-  <si>
-    <t>2026-03-29T18:04:43.185924+03:00</t>
-  </si>
-  <si>
-    <t>2026-03-29T18:04:43.188393+03:00</t>
-  </si>
-  <si>
-    <t>2026-03-29T18:04:43.189354+03:00</t>
-  </si>
-  <si>
-    <t>2026-03-29T18:04:43.190255+03:00</t>
-  </si>
-  <si>
-    <t>2026-03-29T18:04:43.190996+03:00</t>
-  </si>
-  <si>
-    <t>2026-03-29T18:04:43.192001+03:00</t>
-  </si>
-  <si>
-    <t>2026-03-29T18:04:43.192922+03:00</t>
-  </si>
-  <si>
-    <t>2026-03-29T18:04:43.193957+03:00</t>
-  </si>
-  <si>
-    <t>2026-03-29T18:04:43.196371+03:00</t>
-  </si>
-  <si>
-    <t>2026-03-29T18:04:43.198789+03:00</t>
-  </si>
-  <si>
-    <t>2026-03-29T18:04:43.204335+03:00</t>
-  </si>
-  <si>
-    <t>2026-03-29T18:04:43.205345+03:00</t>
-  </si>
-  <si>
-    <t>2026-03-29T18:04:43.208277+03:00</t>
-  </si>
-  <si>
-    <t>2026-03-29T18:04:43.212882+03:00</t>
-  </si>
-  <si>
-    <t>2026-03-29T18:04:43.215867+03:00</t>
-  </si>
-  <si>
-    <t>2026-03-29T18:04:43.218496+03:00</t>
-  </si>
-  <si>
-    <t>2026-03-29T18:04:43.221405+03:00</t>
-  </si>
-  <si>
-    <t>2026-03-29T18:04:43.223743+03:00</t>
-  </si>
-  <si>
-    <t>2026-03-29T18:04:43.226058+03:00</t>
-  </si>
-  <si>
-    <t>2026-03-29T18:04:43.230833+03:00</t>
-  </si>
-  <si>
-    <t>2026-03-29T18:04:43.237293+03:00</t>
-  </si>
-  <si>
-    <t>2026-03-29T18:04:43.239227+03:00</t>
-  </si>
-  <si>
-    <t>2026-03-29T18:04:43.241263+03:00</t>
-  </si>
-  <si>
-    <t>2026-03-29T18:04:43.241964+03:00</t>
-  </si>
-  <si>
-    <t>2026-03-29T18:04:43.245411+03:00</t>
-  </si>
-  <si>
-    <t>2026-03-29T18:04:43.248288+03:00</t>
-  </si>
-  <si>
-    <t>2026-03-29T18:04:43.249831+03:00</t>
-  </si>
-  <si>
-    <t>2026-03-29T18:04:43.252312+03:00</t>
-  </si>
-  <si>
-    <t>2026-03-29T18:04:43.253140+03:00</t>
-  </si>
-  <si>
-    <t>2026-03-29T18:04:43.253798+03:00</t>
-  </si>
-  <si>
-    <t>2026-03-29T18:04:43.254396+03:00</t>
-  </si>
-  <si>
-    <t>2026-03-29T18:04:43.256626+03:00</t>
-  </si>
-  <si>
-    <t>2026-03-29T18:04:43.257564+03:00</t>
-  </si>
-  <si>
-    <t>2026-03-29T18:04:43.258425+03:00</t>
-  </si>
-  <si>
-    <t>2026-03-29T18:04:43.259371+03:00</t>
-  </si>
-  <si>
-    <t>2026-03-29T18:04:43.260444+03:00</t>
-  </si>
-  <si>
-    <t>2026-03-29T18:04:43.263077+03:00</t>
-  </si>
-  <si>
-    <t>2026-03-29T18:04:43.266260+03:00</t>
-  </si>
-  <si>
-    <t>2026-03-29T18:04:43.267795+03:00</t>
-  </si>
-  <si>
-    <t>2026-03-29T18:04:43.273097+03:00</t>
-  </si>
-  <si>
-    <t>2026-03-29T18:04:43.274355+03:00</t>
-  </si>
-  <si>
-    <t>2026-03-29T18:04:43.275247+03:00</t>
-  </si>
-  <si>
-    <t>2026-03-29T18:04:43.276047+03:00</t>
-  </si>
-  <si>
-    <t>2026-03-29T18:04:43.280892+03:00</t>
-  </si>
-  <si>
-    <t>2026-03-29T18:04:43.283110+03:00</t>
-  </si>
-  <si>
-    <t>2026-03-29T18:04:43.285447+03:00</t>
-  </si>
-  <si>
-    <t>2026-03-29T18:04:43.288323+03:00</t>
-  </si>
-  <si>
-    <t>2026-03-29T18:04:43.290420+03:00</t>
-  </si>
-  <si>
-    <t>2026-03-29T18:04:43.292561+03:00</t>
-  </si>
-  <si>
-    <t>2026-03-29T18:04:43.293312+03:00</t>
-  </si>
-  <si>
-    <t>2026-03-29T18:04:43.297895+03:00</t>
-  </si>
-  <si>
-    <t>2026-03-29T18:04:43.302576+03:00</t>
-  </si>
-  <si>
-    <t>2026-03-29T18:04:43.306349+03:00</t>
-  </si>
-  <si>
-    <t>2026-03-29T18:04:43.307041+03:00</t>
-  </si>
-  <si>
-    <t>2026-03-29T18:04:43.308946+03:00</t>
-  </si>
-  <si>
-    <t>2026-03-29T18:04:43.313239+03:00</t>
-  </si>
-  <si>
-    <t>2026-03-29T18:04:43.317220+03:00</t>
-  </si>
-  <si>
-    <t>2026-03-29T18:04:43.319757+03:00</t>
-  </si>
-  <si>
-    <t>2026-03-29T18:04:43.322276+03:00</t>
-  </si>
-  <si>
-    <t>2026-03-29T18:04:43.324170+03:00</t>
-  </si>
-  <si>
-    <t>2026-03-29T18:04:43.324918+03:00</t>
-  </si>
-  <si>
-    <t>2026-03-29T18:04:43.326224+03:00</t>
-  </si>
-  <si>
-    <t>2026-03-29T18:04:43.330502+03:00</t>
-  </si>
-  <si>
-    <t>2026-03-29T18:04:43.335679+03:00</t>
-  </si>
-  <si>
-    <t>2026-03-29T18:04:43.338673+03:00</t>
-  </si>
-  <si>
-    <t>2026-03-29T18:04:43.339604+03:00</t>
-  </si>
-  <si>
-    <t>2026-03-29T18:04:43.340838+03:00</t>
-  </si>
-  <si>
-    <t>2026-03-29T18:04:43.341745+03:00</t>
-  </si>
-  <si>
-    <t>2026-03-29T18:04:43.347346+03:00</t>
-  </si>
-  <si>
-    <t>2026-03-29T18:04:43.349788+03:00</t>
-  </si>
-  <si>
-    <t>2026-03-29T18:04:43.352803+03:00</t>
-  </si>
-  <si>
-    <t>2026-03-29T18:04:43.358922+03:00</t>
-  </si>
-  <si>
-    <t>2026-03-29T18:04:43.363182+03:00</t>
-  </si>
-  <si>
-    <t>2026-03-29T18:04:43.367942+03:00</t>
-  </si>
-  <si>
-    <t>2026-03-29T18:04:43.370143+03:00</t>
-  </si>
-  <si>
-    <t>2026-03-29T18:04:43.372771+03:00</t>
-  </si>
-  <si>
-    <t>2026-03-29T18:04:43.375071+03:00</t>
-  </si>
-  <si>
-    <t>2026-03-29T18:04:43.378507+03:00</t>
-  </si>
-  <si>
-    <t>2026-03-29T18:04:43.383052+03:00</t>
-  </si>
-  <si>
-    <t>2026-03-29T18:04:43.387208+03:00</t>
-  </si>
-  <si>
-    <t>2026-03-29T18:04:43.388098+03:00</t>
-  </si>
-  <si>
-    <t>2026-03-29T18:04:43.388838+03:00</t>
-  </si>
-  <si>
-    <t>2026-03-29T18:04:43.391330+03:00</t>
-  </si>
-  <si>
-    <t>2026-03-29T18:04:43.393572+03:00</t>
-  </si>
-  <si>
-    <t>2026-03-29T18:04:43.398708+03:00</t>
-  </si>
-  <si>
-    <t>2026-03-29T18:04:43.402785+03:00</t>
-  </si>
-  <si>
-    <t>2026-03-29T18:04:43.406384+03:00</t>
-  </si>
-  <si>
-    <t>2026-03-29T18:04:43.408509+03:00</t>
-  </si>
-  <si>
-    <t>2026-03-29T18:04:43.410886+03:00</t>
-  </si>
-  <si>
-    <t>2026-03-29T18:04:43.416339+03:00</t>
-  </si>
-  <si>
-    <t>2026-03-29T18:04:43.420845+03:00</t>
-  </si>
-  <si>
-    <t>2026-03-29T18:04:43.421628+03:00</t>
-  </si>
-  <si>
-    <t>2026-03-29T18:04:43.423692+03:00</t>
-  </si>
-  <si>
-    <t>2026-03-29T18:04:43.425623+03:00</t>
-  </si>
-  <si>
-    <t>2026-03-29T18:04:43.429719+03:00</t>
-  </si>
-  <si>
-    <t>2026-03-29T18:04:43.434253+03:00</t>
-  </si>
-  <si>
-    <t>2026-03-29T18:04:43.436811+03:00</t>
-  </si>
-  <si>
-    <t>2026-03-29T18:04:43.437981+03:00</t>
-  </si>
-  <si>
-    <t>2026-03-29T18:04:43.438602+03:00</t>
-  </si>
-  <si>
-    <t>2026-03-29T18:04:43.440675+03:00</t>
-  </si>
-  <si>
-    <t>2026-03-29T18:04:43.442617+03:00</t>
-  </si>
-  <si>
-    <t>2026-03-29T18:04:43.447451+03:00</t>
-  </si>
-  <si>
-    <t>2026-03-29T18:04:43.450280+03:00</t>
-  </si>
-  <si>
-    <t>2026-03-29T18:04:43.452133+03:00</t>
-  </si>
-  <si>
-    <t>2026-03-29T18:04:43.455813+03:00</t>
-  </si>
-  <si>
-    <t>2026-03-29T18:04:43.456662+03:00</t>
-  </si>
-  <si>
-    <t>2026-03-29T18:04:43.457580+03:00</t>
-  </si>
-  <si>
-    <t>2026-03-29T18:04:43.458422+03:00</t>
-  </si>
-  <si>
-    <t>2026-03-29T18:04:43.569761+03:00</t>
+    <t>2026-03-29T22:06:38.515993+03:00</t>
+  </si>
+  <si>
+    <t>2026-03-29T22:06:38.640570+03:00</t>
+  </si>
+  <si>
+    <t>2026-03-29T22:06:38.642548+03:00</t>
+  </si>
+  <si>
+    <t>2026-03-29T22:06:38.754591+03:00</t>
+  </si>
+  <si>
+    <t>2026-03-29T22:06:38.891047+03:00</t>
+  </si>
+  <si>
+    <t>2026-03-29T22:06:39.018559+03:00</t>
+  </si>
+  <si>
+    <t>2026-03-29T22:06:39.142946+03:00</t>
+  </si>
+  <si>
+    <t>2026-03-29T22:06:39.252076+03:00</t>
+  </si>
+  <si>
+    <t>2026-03-29T22:06:39.405301+03:00</t>
+  </si>
+  <si>
+    <t>2026-03-29T22:06:39.528124+03:00</t>
+  </si>
+  <si>
+    <t>2026-03-29T22:06:39.530410+03:00</t>
+  </si>
+  <si>
+    <t>2026-03-29T22:06:39.532267+03:00</t>
+  </si>
+  <si>
+    <t>2026-03-29T22:06:39.533864+03:00</t>
+  </si>
+  <si>
+    <t>2026-03-29T22:06:39.534934+03:00</t>
+  </si>
+  <si>
+    <t>2026-03-29T22:06:39.634695+03:00</t>
+  </si>
+  <si>
+    <t>2026-03-29T22:06:39.747525+03:00</t>
+  </si>
+  <si>
+    <t>2026-03-29T22:06:39.884556+03:00</t>
+  </si>
+  <si>
+    <t>2026-03-29T22:06:40.001008+03:00</t>
+  </si>
+  <si>
+    <t>2026-03-29T22:06:40.126285+03:00</t>
+  </si>
+  <si>
+    <t>2026-03-29T22:06:40.267288+03:00</t>
+  </si>
+  <si>
+    <t>2026-03-29T22:06:40.269809+03:00</t>
+  </si>
+  <si>
+    <t>2026-03-29T22:06:40.271627+03:00</t>
+  </si>
+  <si>
+    <t>2026-03-29T22:06:40.413200+03:00</t>
+  </si>
+  <si>
+    <t>2026-03-29T22:06:40.539211+03:00</t>
+  </si>
+  <si>
+    <t>2026-03-29T22:06:40.646094+03:00</t>
+  </si>
+  <si>
+    <t>2026-03-29T22:06:40.764924+03:00</t>
+  </si>
+  <si>
+    <t>2026-03-29T22:06:40.883485+03:00</t>
+  </si>
+  <si>
+    <t>2026-03-29T22:06:40.989641+03:00</t>
+  </si>
+  <si>
+    <t>2026-03-29T22:06:40.991240+03:00</t>
+  </si>
+  <si>
+    <t>2026-03-29T22:06:41.066324+03:00</t>
+  </si>
+  <si>
+    <t>2026-03-29T22:06:41.113169+03:00</t>
+  </si>
+  <si>
+    <t>2026-03-29T22:06:41.114834+03:00</t>
+  </si>
+  <si>
+    <t>2026-03-29T22:06:41.117274+03:00</t>
+  </si>
+  <si>
+    <t>2026-03-29T22:06:41.237350+03:00</t>
+  </si>
+  <si>
+    <t>2026-03-29T22:06:41.328313+03:00</t>
+  </si>
+  <si>
+    <t>2026-03-29T22:06:41.414271+03:00</t>
+  </si>
+  <si>
+    <t>2026-03-29T22:06:41.458240+03:00</t>
+  </si>
+  <si>
+    <t>2026-03-29T22:06:41.460447+03:00</t>
+  </si>
+  <si>
+    <t>2026-03-29T22:06:41.574984+03:00</t>
+  </si>
+  <si>
+    <t>2026-03-29T22:06:41.577178+03:00</t>
+  </si>
+  <si>
+    <t>2026-03-29T22:06:41.633040+03:00</t>
+  </si>
+  <si>
+    <t>2026-03-29T22:06:41.752979+03:00</t>
+  </si>
+  <si>
+    <t>2026-03-29T22:06:41.851173+03:00</t>
+  </si>
+  <si>
+    <t>2026-03-29T22:06:41.899764+03:00</t>
+  </si>
+  <si>
+    <t>2026-03-29T22:06:42.017534+03:00</t>
+  </si>
+  <si>
+    <t>2026-03-29T22:06:42.063763+03:00</t>
+  </si>
+  <si>
+    <t>2026-03-29T22:06:42.066326+03:00</t>
+  </si>
+  <si>
+    <t>2026-03-29T22:06:42.211687+03:00</t>
+  </si>
+  <si>
+    <t>2026-03-29T22:06:42.325081+03:00</t>
+  </si>
+  <si>
+    <t>2026-03-29T22:06:42.443621+03:00</t>
+  </si>
+  <si>
+    <t>2026-03-29T22:06:42.576403+03:00</t>
+  </si>
+  <si>
+    <t>2026-03-29T22:06:42.623235+03:00</t>
+  </si>
+  <si>
+    <t>2026-03-29T22:06:42.729521+03:00</t>
+  </si>
+  <si>
+    <t>2026-03-29T22:06:42.732048+03:00</t>
+  </si>
+  <si>
+    <t>2026-03-29T22:06:42.776220+03:00</t>
+  </si>
+  <si>
+    <t>2026-03-29T22:06:42.778308+03:00</t>
+  </si>
+  <si>
+    <t>2026-03-29T22:06:42.872777+03:00</t>
+  </si>
+  <si>
+    <t>2026-03-29T22:06:42.976448+03:00</t>
+  </si>
+  <si>
+    <t>2026-03-29T22:06:43.075664+03:00</t>
+  </si>
+  <si>
+    <t>2026-03-29T22:06:43.179589+03:00</t>
+  </si>
+  <si>
+    <t>2026-03-29T22:06:43.292892+03:00</t>
+  </si>
+  <si>
+    <t>2026-03-29T22:06:43.337758+03:00</t>
+  </si>
+  <si>
+    <t>2026-03-29T22:06:43.380162+03:00</t>
+  </si>
+  <si>
+    <t>2026-03-29T22:06:43.499404+03:00</t>
+  </si>
+  <si>
+    <t>2026-03-29T22:06:43.597368+03:00</t>
+  </si>
+  <si>
+    <t>2026-03-29T22:06:43.598739+03:00</t>
+  </si>
+  <si>
+    <t>2026-03-29T22:06:43.727793+03:00</t>
+  </si>
+  <si>
+    <t>2026-03-29T22:06:43.831992+03:00</t>
+  </si>
+  <si>
+    <t>2026-03-29T22:06:43.833491+03:00</t>
+  </si>
+  <si>
+    <t>2026-03-29T22:06:43.873571+03:00</t>
+  </si>
+  <si>
+    <t>2026-03-29T22:06:44.052446+03:00</t>
+  </si>
+  <si>
+    <t>2026-03-29T22:06:44.174169+03:00</t>
+  </si>
+  <si>
+    <t>2026-03-29T22:06:44.216469+03:00</t>
+  </si>
+  <si>
+    <t>2026-03-29T22:06:44.351820+03:00</t>
+  </si>
+  <si>
+    <t>2026-03-29T22:06:44.466475+03:00</t>
+  </si>
+  <si>
+    <t>2026-03-29T22:06:44.516584+03:00</t>
+  </si>
+  <si>
+    <t>2026-03-29T22:06:44.631259+03:00</t>
+  </si>
+  <si>
+    <t>2026-03-29T22:06:44.749081+03:00</t>
+  </si>
+  <si>
+    <t>2026-03-29T22:06:44.866048+03:00</t>
+  </si>
+  <si>
+    <t>2026-03-29T22:06:44.993540+03:00</t>
+  </si>
+  <si>
+    <t>2026-03-29T22:06:45.101264+03:00</t>
+  </si>
+  <si>
+    <t>2026-03-29T22:06:45.210379+03:00</t>
+  </si>
+  <si>
+    <t>2026-03-29T22:06:45.334430+03:00</t>
+  </si>
+  <si>
+    <t>2026-03-29T22:06:45.464378+03:00</t>
+  </si>
+  <si>
+    <t>2026-03-29T22:06:45.506921+03:00</t>
+  </si>
+  <si>
+    <t>2026-03-29T22:06:45.563610+03:00</t>
+  </si>
+  <si>
+    <t>2026-03-29T22:06:45.610515+03:00</t>
+  </si>
+  <si>
+    <t>2026-03-29T22:06:45.612332+03:00</t>
+  </si>
+  <si>
+    <t>2026-03-29T22:06:45.658560+03:00</t>
+  </si>
+  <si>
+    <t>2026-03-29T22:06:45.701099+03:00</t>
+  </si>
+  <si>
+    <t>2026-03-29T22:06:45.811312+03:00</t>
+  </si>
+  <si>
+    <t>2026-03-29T22:06:45.922649+03:00</t>
+  </si>
+  <si>
+    <t>2026-03-29T22:06:46.061122+03:00</t>
+  </si>
+  <si>
+    <t>2026-03-29T22:06:46.065934+03:00</t>
+  </si>
+  <si>
+    <t>2026-03-29T22:06:46.166147+03:00</t>
+  </si>
+  <si>
+    <t>2026-03-29T22:06:46.302642+03:00</t>
+  </si>
+  <si>
+    <t>2026-03-29T22:06:46.422719+03:00</t>
+  </si>
+  <si>
+    <t>2026-03-29T22:06:46.467472+03:00</t>
+  </si>
+  <si>
+    <t>2026-03-29T22:06:46.608596+03:00</t>
+  </si>
+  <si>
+    <t>2026-03-29T22:06:46.759762+03:00</t>
+  </si>
+  <si>
+    <t>2026-03-29T22:06:46.805721+03:00</t>
+  </si>
+  <si>
+    <t>2026-03-29T22:06:46.853075+03:00</t>
+  </si>
+  <si>
+    <t>2026-03-29T22:06:46.854757+03:00</t>
+  </si>
+  <si>
+    <t>2026-03-29T22:06:46.899389+03:00</t>
+  </si>
+  <si>
+    <t>2026-03-29T22:06:46.901583+03:00</t>
+  </si>
+  <si>
+    <t>2026-03-29T22:06:46.903249+03:00</t>
+  </si>
+  <si>
+    <t>2026-03-29T22:06:46.905541+03:00</t>
+  </si>
+  <si>
+    <t>2026-03-29T22:06:46.908283+03:00</t>
+  </si>
+  <si>
+    <t>2026-03-29T22:06:47.018350+03:00</t>
+  </si>
+  <si>
+    <t>2026-03-29T22:06:47.019777+03:00</t>
+  </si>
+  <si>
+    <t>2026-03-29T22:06:47.116759+03:00</t>
+  </si>
+  <si>
+    <t>2026-03-29T22:06:47.211602+03:00</t>
+  </si>
+  <si>
+    <t>2026-03-29T22:06:47.254062+03:00</t>
+  </si>
+  <si>
+    <t>2026-03-29T22:06:47.256013+03:00</t>
+  </si>
+  <si>
+    <t>2026-03-29T22:06:47.348210+03:00</t>
+  </si>
+  <si>
+    <t>2026-03-29T22:06:47.482806+03:00</t>
+  </si>
+  <si>
+    <t>2026-03-29T22:06:47.593295+03:00</t>
+  </si>
+  <si>
+    <t>2026-03-29T22:06:47.731828+03:00</t>
+  </si>
+  <si>
+    <t>2026-03-29T22:06:47.843947+03:00</t>
+  </si>
+  <si>
+    <t>2026-03-29T22:06:47.997014+03:00</t>
+  </si>
+  <si>
+    <t>2026-03-29T22:06:48.107451+03:00</t>
+  </si>
+  <si>
+    <t>2026-03-29T22:06:48.148510+03:00</t>
+  </si>
+  <si>
+    <t>2026-03-29T22:06:48.240708+03:00</t>
+  </si>
+  <si>
+    <t>2026-03-29T22:06:48.280449+03:00</t>
+  </si>
+  <si>
+    <t>2026-03-29T22:06:48.322439+03:00</t>
+  </si>
+  <si>
+    <t>2026-03-29T22:06:48.363933+03:00</t>
+  </si>
+  <si>
+    <t>2026-03-29T22:06:48.365174+03:00</t>
+  </si>
+  <si>
+    <t>2026-03-29T22:06:48.408395+03:00</t>
+  </si>
+  <si>
+    <t>2026-03-29T22:06:48.409626+03:00</t>
+  </si>
+  <si>
+    <t>2026-03-29T22:06:48.507577+03:00</t>
+  </si>
+  <si>
+    <t>2026-03-29T22:06:48.549098+03:00</t>
+  </si>
+  <si>
+    <t>2026-03-29T22:06:48.551226+03:00</t>
+  </si>
+  <si>
+    <t>2026-03-29T22:06:48.553221+03:00</t>
+  </si>
+  <si>
+    <t>2026-03-29T22:06:48.555132+03:00</t>
+  </si>
+  <si>
+    <t>2026-03-29T22:06:48.556992+03:00</t>
+  </si>
+  <si>
+    <t>2026-03-29T22:06:48.558846+03:00</t>
+  </si>
+  <si>
+    <t>2026-03-29T22:06:48.560299+03:00</t>
+  </si>
+  <si>
+    <t>2026-03-29T22:06:48.681659+03:00</t>
+  </si>
+  <si>
+    <t>2026-03-29T22:06:48.684534+03:00</t>
+  </si>
+  <si>
+    <t>2026-03-29T22:06:48.686477+03:00</t>
+  </si>
+  <si>
+    <t>2026-03-29T22:06:48.734544+03:00</t>
+  </si>
+  <si>
+    <t>2026-03-29T22:06:48.833022+03:00</t>
+  </si>
+  <si>
+    <t>2026-03-29T22:06:48.834261+03:00</t>
+  </si>
+  <si>
+    <t>2026-03-29T22:06:48.883370+03:00</t>
+  </si>
+  <si>
+    <t>2026-03-29T22:06:48.974254+03:00</t>
+  </si>
+  <si>
+    <t>2026-03-29T22:06:49.074743+03:00</t>
+  </si>
+  <si>
+    <t>2026-03-29T22:06:49.187376+03:00</t>
+  </si>
+  <si>
+    <t>2026-03-29T22:06:49.190636+03:00</t>
+  </si>
+  <si>
+    <t>2026-03-29T22:06:49.312050+03:00</t>
+  </si>
+  <si>
+    <t>2026-03-29T22:06:49.425067+03:00</t>
+  </si>
+  <si>
+    <t>2026-03-29T22:06:49.546524+03:00</t>
+  </si>
+  <si>
+    <t>2026-03-29T22:06:49.547942+03:00</t>
+  </si>
+  <si>
+    <t>2026-03-29T22:06:49.668180+03:00</t>
+  </si>
+  <si>
+    <t>2026-03-29T22:06:49.787212+03:00</t>
+  </si>
+  <si>
+    <t>2026-03-29T22:06:50.015111+03:00</t>
+  </si>
+  <si>
+    <t>2026-03-29T22:06:50.018192+03:00</t>
+  </si>
+  <si>
+    <t>2026-03-29T22:06:50.154679+03:00</t>
+  </si>
+  <si>
+    <t>2026-03-29T22:06:50.290164+03:00</t>
+  </si>
+  <si>
+    <t>2026-03-29T22:06:50.335299+03:00</t>
+  </si>
+  <si>
+    <t>2026-03-29T22:06:50.410081+03:00</t>
+  </si>
+  <si>
+    <t>2026-03-29T22:06:50.512638+03:00</t>
+  </si>
+  <si>
+    <t>2026-03-29T22:06:50.623489+03:00</t>
+  </si>
+  <si>
+    <t>2026-03-29T22:06:50.737359+03:00</t>
+  </si>
+  <si>
+    <t>2026-03-29T22:06:50.739062+03:00</t>
+  </si>
+  <si>
+    <t>2026-03-29T22:06:50.803953+03:00</t>
+  </si>
+  <si>
+    <t>2026-03-29T22:06:50.806283+03:00</t>
+  </si>
+  <si>
+    <t>2026-03-29T22:06:50.924898+03:00</t>
+  </si>
+  <si>
+    <t>2026-03-29T22:06:50.926010+03:00</t>
+  </si>
+  <si>
+    <t>2026-03-29T22:06:51.044279+03:00</t>
+  </si>
+  <si>
+    <t>2026-03-29T22:06:51.153537+03:00</t>
+  </si>
+  <si>
+    <t>2026-03-29T22:06:51.298652+03:00</t>
+  </si>
+  <si>
+    <t>2026-03-29T22:06:51.425100+03:00</t>
+  </si>
+  <si>
+    <t>2026-03-29T22:06:51.471797+03:00</t>
+  </si>
+  <si>
+    <t>2026-03-29T22:06:51.598350+03:00</t>
+  </si>
+  <si>
+    <t>2026-03-29T22:06:51.707243+03:00</t>
+  </si>
+  <si>
+    <t>2026-03-29T22:06:51.812775+03:00</t>
+  </si>
+  <si>
+    <t>2026-03-29T22:06:51.944597+03:00</t>
+  </si>
+  <si>
+    <t>2026-03-29T22:06:52.103653+03:00</t>
+  </si>
+  <si>
+    <t>2026-03-29T22:06:52.149121+03:00</t>
+  </si>
+  <si>
+    <t>2026-03-29T22:06:52.192978+03:00</t>
+  </si>
+  <si>
+    <t>2026-03-29T22:06:52.329999+03:00</t>
+  </si>
+  <si>
+    <t>2026-03-29T22:06:52.444486+03:00</t>
+  </si>
+  <si>
+    <t>2026-03-29T22:06:52.565865+03:00</t>
+  </si>
+  <si>
+    <t>2026-03-29T22:06:52.694006+03:00</t>
+  </si>
+  <si>
+    <t>2026-03-29T22:06:52.829224+03:00</t>
+  </si>
+  <si>
+    <t>2026-03-29T22:06:52.946899+03:00</t>
+  </si>
+  <si>
+    <t>2026-03-29T22:06:53.081263+03:00</t>
+  </si>
+  <si>
+    <t>2026-03-29T22:06:53.216101+03:00</t>
+  </si>
+  <si>
+    <t>2026-03-29T22:06:53.326961+03:00</t>
+  </si>
+  <si>
+    <t>2026-03-29T22:06:53.328728+03:00</t>
+  </si>
+  <si>
+    <t>2026-03-29T22:06:53.447897+03:00</t>
+  </si>
+  <si>
+    <t>2026-03-29T22:06:53.554045+03:00</t>
+  </si>
+  <si>
+    <t>2026-03-29T22:06:53.670832+03:00</t>
+  </si>
+  <si>
+    <t>2026-03-29T22:06:53.793196+03:00</t>
+  </si>
+  <si>
+    <t>2026-03-29T22:06:53.794931+03:00</t>
+  </si>
+  <si>
+    <t>2026-03-29T22:06:53.796678+03:00</t>
+  </si>
+  <si>
+    <t>2026-03-29T22:06:53.798468+03:00</t>
+  </si>
+  <si>
+    <t>2026-03-29T22:06:53.941242+03:00</t>
+  </si>
+  <si>
+    <t>2026-03-29T22:06:54.047226+03:00</t>
+  </si>
+  <si>
+    <t>2026-03-29T22:06:54.180542+03:00</t>
+  </si>
+  <si>
+    <t>2026-03-29T22:06:54.183197+03:00</t>
+  </si>
+  <si>
+    <t>2026-03-29T22:06:54.186029+03:00</t>
+  </si>
+  <si>
+    <t>2026-03-29T22:06:54.303546+03:00</t>
+  </si>
+  <si>
+    <t>2026-03-29T22:06:54.306320+03:00</t>
+  </si>
+  <si>
+    <t>2026-03-29T22:06:54.308929+03:00</t>
+  </si>
+  <si>
+    <t>2026-03-29T22:06:54.311013+03:00</t>
+  </si>
+  <si>
+    <t>2026-03-29T22:06:54.422403+03:00</t>
   </si>
 </sst>
 </file>
